--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA280"/>
+  <dimension ref="A1:AA281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -27953,6 +27953,103 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Svam Group, Ooo</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Svam Group, Ooo</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Solntsevo</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>9, стр.1 Novomeshcherskiy Proyezd</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>119619</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>https://svamgroup.ru</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>info@svamgroup.ru</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 989-24-14</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>40477522</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr"/>
+      <c r="S281" s="2" t="inlineStr"/>
+      <c r="T281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>Slava Kuzmenko</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/slava-kuzmenko-0466a67/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Russia.xlsx
+++ b/BWI/bestwine_output/bestwine_Russia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA281"/>
+  <dimension ref="A1:AA282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -28050,6 +28050,103 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Svam Group, Ooo</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Svam Group, Ooo</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Moskva, Solntsevo</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>9, стр.1 Novomeshcherskiy Proyezd</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>119619</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://svamgroup.ru</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>info@svamgroup.ru</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>+7 495 989-24-14</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>40477522</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr"/>
+      <c r="S282" s="2" t="inlineStr"/>
+      <c r="T282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
+          <t>Slava Kuzmenko</t>
+        </is>
+      </c>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/slava-kuzmenko-0466a67/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
